--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>91.480003</v>
+        <v>93.269997</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>93.269997</v>
+        <v>95.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>95.75</v>
+        <v>99.300003</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>99.300003</v>
+        <v>98.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>98.75</v>
+        <v>99.050003</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>99.050003</v>
+        <v>100.050003</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>100.050003</v>
+        <v>102.970001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>102.970001</v>
+        <v>103.730003</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>103.730003</v>
+        <v>103.169998</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>103.169998</v>
+        <v>100.389999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>100.389999</v>
+        <v>97.860001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>97.860001</v>
+        <v>100.300003</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>100.300003</v>
+        <v>96.08000199999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>96.08000199999999</v>
+        <v>92.339996</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>92.339996</v>
+        <v>90.910004</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>90.910004</v>
+        <v>90.699997</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>90.699997</v>
+        <v>92.099998</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>92.099998</v>
+        <v>94.66999800000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>94.66999800000001</v>
+        <v>94.720001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>94.720001</v>
+        <v>94.099998</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>94.099998</v>
+        <v>92.410004</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>92.410004</v>
+        <v>92.589996</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>92.589996</v>
+        <v>92.55999799999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>92.55999799999999</v>
+        <v>90.720001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>90.720001</v>
+        <v>90.44000200000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>90.44000200000001</v>
+        <v>91.379997</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -434,490 +434,490 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="B2" t="n">
-        <v>75.029999</v>
+        <v>83.56999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B3" t="n">
-        <v>83.56999999999999</v>
+        <v>66.18000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B4" t="n">
-        <v>66.18000000000001</v>
+        <v>75.209999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B5" t="n">
-        <v>75.209999</v>
+        <v>88.150002</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B6" t="n">
-        <v>88.150002</v>
+        <v>95.720001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B7" t="n">
-        <v>95.720001</v>
+        <v>100.279999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B8" t="n">
-        <v>100.279999</v>
+        <v>104.690002</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B9" t="n">
-        <v>104.690002</v>
+        <v>114.669998</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B10" t="n">
-        <v>114.669998</v>
+        <v>105.760002</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B11" t="n">
-        <v>105.760002</v>
+        <v>98.620003</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B12" t="n">
-        <v>98.620003</v>
+        <v>89.550003</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B13" t="n">
-        <v>89.550003</v>
+        <v>79.489998</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B14" t="n">
-        <v>79.489998</v>
+        <v>86.529999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B15" t="n">
-        <v>86.529999</v>
+        <v>80.550003</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B16" t="n">
-        <v>80.550003</v>
+        <v>80.260002</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B17" t="n">
-        <v>80.260002</v>
+        <v>78.870003</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B18" t="n">
-        <v>78.870003</v>
+        <v>77.050003</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B19" t="n">
-        <v>77.050003</v>
+        <v>75.66999800000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B20" t="n">
-        <v>75.66999800000001</v>
+        <v>76.779999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B21" t="n">
-        <v>76.779999</v>
+        <v>68.089996</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B22" t="n">
-        <v>68.089996</v>
+        <v>70.639999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B23" t="n">
-        <v>70.639999</v>
+        <v>81.800003</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B24" t="n">
-        <v>81.800003</v>
+        <v>83.629997</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B25" t="n">
-        <v>83.629997</v>
+        <v>90.790001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B26" t="n">
-        <v>90.790001</v>
+        <v>81.019997</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B27" t="n">
-        <v>81.019997</v>
+        <v>75.959999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B28" t="n">
-        <v>75.959999</v>
+        <v>71.650002</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B29" t="n">
-        <v>71.650002</v>
+        <v>75.849998</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B30" t="n">
-        <v>75.849998</v>
+        <v>78.260002</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B31" t="n">
-        <v>78.260002</v>
+        <v>83.16999800000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B32" t="n">
-        <v>83.16999800000001</v>
+        <v>81.93000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B33" t="n">
-        <v>81.93000000000001</v>
+        <v>76.989998</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B34" t="n">
-        <v>76.989998</v>
+        <v>81.540001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B35" t="n">
-        <v>81.540001</v>
+        <v>77.910004</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B36" t="n">
-        <v>77.910004</v>
+        <v>73.550003</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B37" t="n">
-        <v>73.550003</v>
+        <v>68.16999800000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B38" t="n">
-        <v>68.16999800000001</v>
+        <v>69.260002</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B39" t="n">
-        <v>69.260002</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B40" t="n">
-        <v>68</v>
+        <v>71.720001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B41" t="n">
-        <v>71.720001</v>
+        <v>72.529999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>72.529999</v>
+        <v>69.760002</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B43" t="n">
-        <v>69.760002</v>
+        <v>71.480003</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B44" t="n">
-        <v>71.480003</v>
+        <v>58.209999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B45" t="n">
-        <v>58.209999</v>
+        <v>60.790001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B46" t="n">
-        <v>60.790001</v>
+        <v>65.110001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B47" t="n">
-        <v>65.110001</v>
+        <v>69.260002</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B48" t="n">
-        <v>69.260002</v>
+        <v>64.010002</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B49" t="n">
-        <v>64.010002</v>
+        <v>62.369999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B50" t="n">
-        <v>62.369999</v>
+        <v>60.98</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B51" t="n">
-        <v>60.98</v>
+        <v>58.549999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B52" t="n">
-        <v>58.549999</v>
+        <v>57.419998</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B53" t="n">
-        <v>57.419998</v>
+        <v>65.209999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B54" t="n">
-        <v>65.209999</v>
+        <v>67.019997</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B55" t="n">
-        <v>67.019997</v>
+        <v>101.379997</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B56" t="n">
-        <v>101.379997</v>
+        <v>105.07</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B57" t="n">
-        <v>105.07</v>
+        <v>87.360001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B58" t="n">
-        <v>87.360001</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B59" t="n">
-        <v>69.5</v>
+        <v>84.66999800000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B60" t="n">
-        <v>84.66999800000001</v>
+        <v>85.760002</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>85.760002</v>
+        <v>90.41999800000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>91.379997</v>
+        <v>91.910004</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>91.910004</v>
+        <v>90.81999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>90.81999999999999</v>
+        <v>90.970001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>90.970001</v>
+        <v>91.110001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>91.110001</v>
+        <v>88.980003</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>88.980003</v>
+        <v>89.220001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>89.220001</v>
+        <v>88.779999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>88.779999</v>
+        <v>91.05999799999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>91.05999799999999</v>
+        <v>90.800003</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>90.800003</v>
+        <v>91.480003</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>91.480003</v>
+        <v>91.199997</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>91.199997</v>
+        <v>91.849998</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>91.849998</v>
+        <v>93.55999799999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>93.55999799999999</v>
+        <v>93.540001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>93.540001</v>
+        <v>94.290001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>94.290001</v>
+        <v>95.31999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>95.31999999999999</v>
+        <v>94.93000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>94.93000000000001</v>
+        <v>95.040001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>95.040001</v>
+        <v>95.589996</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>95.589996</v>
+        <v>101.410004</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>101.410004</v>
+        <v>99.019997</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>99.019997</v>
+        <v>98.599998</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>98.599998</v>
+        <v>96.30999799999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>96.30999799999999</v>
+        <v>97.800003</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>97.800003</v>
+        <v>98.410004</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>98.410004</v>
+        <v>102.190002</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>102.190002</v>
+        <v>103.269997</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>103.269997</v>
+        <v>102.870003</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>102.870003</v>
+        <v>100.040001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>100.040001</v>
+        <v>103.459999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>103.459999</v>
+        <v>100.889999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,490 +434,482 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B2" t="n">
-        <v>83.56999999999999</v>
+        <v>66.18000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B3" t="n">
-        <v>66.18000000000001</v>
+        <v>75.209999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B4" t="n">
-        <v>75.209999</v>
+        <v>88.150002</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B5" t="n">
-        <v>88.150002</v>
+        <v>95.720001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B6" t="n">
-        <v>95.720001</v>
+        <v>100.279999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B7" t="n">
-        <v>100.279999</v>
+        <v>104.690002</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B8" t="n">
-        <v>104.690002</v>
+        <v>114.669998</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B9" t="n">
-        <v>114.669998</v>
+        <v>105.760002</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B10" t="n">
-        <v>105.760002</v>
+        <v>98.620003</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B11" t="n">
-        <v>98.620003</v>
+        <v>89.550003</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B12" t="n">
-        <v>89.550003</v>
+        <v>79.489998</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B13" t="n">
-        <v>79.489998</v>
+        <v>86.529999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B14" t="n">
-        <v>86.529999</v>
+        <v>80.550003</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B15" t="n">
-        <v>80.550003</v>
+        <v>80.260002</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B16" t="n">
-        <v>80.260002</v>
+        <v>78.870003</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B17" t="n">
-        <v>78.870003</v>
+        <v>77.050003</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B18" t="n">
-        <v>77.050003</v>
+        <v>75.66999800000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B19" t="n">
-        <v>75.66999800000001</v>
+        <v>76.779999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B20" t="n">
-        <v>76.779999</v>
+        <v>68.089996</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B21" t="n">
-        <v>68.089996</v>
+        <v>70.639999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B22" t="n">
-        <v>70.639999</v>
+        <v>81.800003</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B23" t="n">
-        <v>81.800003</v>
+        <v>83.629997</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B24" t="n">
-        <v>83.629997</v>
+        <v>90.790001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B25" t="n">
-        <v>90.790001</v>
+        <v>81.019997</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B26" t="n">
-        <v>81.019997</v>
+        <v>75.959999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B27" t="n">
-        <v>75.959999</v>
+        <v>71.650002</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B28" t="n">
-        <v>71.650002</v>
+        <v>75.849998</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B29" t="n">
-        <v>75.849998</v>
+        <v>78.260002</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B30" t="n">
-        <v>78.260002</v>
+        <v>83.16999800000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B31" t="n">
-        <v>83.16999800000001</v>
+        <v>81.93000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B32" t="n">
-        <v>81.93000000000001</v>
+        <v>76.989998</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B33" t="n">
-        <v>76.989998</v>
+        <v>81.540001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B34" t="n">
-        <v>81.540001</v>
+        <v>77.910004</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B35" t="n">
-        <v>77.910004</v>
+        <v>73.550003</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B36" t="n">
-        <v>73.550003</v>
+        <v>68.16999800000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B37" t="n">
-        <v>68.16999800000001</v>
+        <v>69.260002</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B38" t="n">
-        <v>69.260002</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B39" t="n">
-        <v>68</v>
+        <v>71.720001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B40" t="n">
-        <v>71.720001</v>
+        <v>72.529999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B41" t="n">
-        <v>72.529999</v>
+        <v>69.760002</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B42" t="n">
-        <v>69.760002</v>
+        <v>71.480003</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B43" t="n">
-        <v>71.480003</v>
+        <v>58.209999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B44" t="n">
-        <v>58.209999</v>
+        <v>60.790001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B45" t="n">
-        <v>60.790001</v>
+        <v>65.110001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B46" t="n">
-        <v>65.110001</v>
+        <v>69.260002</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B47" t="n">
-        <v>69.260002</v>
+        <v>64.010002</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B48" t="n">
-        <v>64.010002</v>
+        <v>62.369999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B49" t="n">
-        <v>62.369999</v>
+        <v>60.98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B50" t="n">
-        <v>60.98</v>
+        <v>58.549999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B51" t="n">
-        <v>58.549999</v>
+        <v>57.419998</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B52" t="n">
-        <v>57.419998</v>
+        <v>65.209999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B53" t="n">
-        <v>65.209999</v>
+        <v>67.019997</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B54" t="n">
-        <v>67.019997</v>
+        <v>101.379997</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B55" t="n">
-        <v>101.379997</v>
+        <v>105.07</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B56" t="n">
-        <v>105.07</v>
+        <v>87.360001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B57" t="n">
-        <v>87.360001</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B58" t="n">
-        <v>69.5</v>
+        <v>84.66999800000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B59" t="n">
-        <v>84.66999800000001</v>
+        <v>85.760002</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="B60" t="n">
-        <v>85.760002</v>
+        <v>90.41999800000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>90.41999800000001</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>46326</v>
-      </c>
-      <c r="B62" t="n">
-        <v>100.889999</v>
+        <v>104.360001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_petroleo_wti.xlsx
+++ b/data/final/series/yahoo_petroleo_wti.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>104.360001</v>
+        <v>104.120003</v>
       </c>
     </row>
   </sheetData>
